--- a/outputs/miq-import/miq_manual_review.xlsx
+++ b/outputs/miq-import/miq_manual_review.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qaydalar" sheetId="1" r:id="Rf82670261d294730"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stars_review" sheetId="2" r:id="Rc872f95f9cf44881"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nesimi_review" sheetId="3" r:id="Ra092dcc86ad54057"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qurtulus_review" sheetId="4" r:id="R967350f242654c6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qaydalar" sheetId="1" r:id="R81dc66a19c2c4d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stars_review" sheetId="2" r:id="R56b53625eb784c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nesimi_review" sheetId="3" r:id="Rf80535a37f1c4ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qurtulus_review" sheetId="4" r:id="R10052b7671284cdc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -66,7 +66,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -100,6 +100,9 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -371,6 +374,14 @@
         <x:v>Bu fayldakı adlar avtomatik importa daxil edilməyib; teacher_id yalnız əl ilə təsdiqdən sonra seçilməlidir.</x:v>
       </x:c>
     </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="16" t="str">
+        <x:v>Dil + ədəbiyyat qaydası</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>Azərbaycan dili və Rus dili 40 bal, ədəbiyyat 20 bal üzərindən qiymətləndirilir. Cüt nəticədə ədəbiyyat balı əvvəlcə ×2 edilərək 40 şkalasına gətirilir, sonra ədədi orta hesablanır.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:B1"/>
@@ -500,7 +511,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re01a6f9c4c1b4e84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39e85a5b7e494d18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -646,7 +657,7 @@
         <x:v>nesimi-teacher-sema-avilova-fazil-qizi</x:v>
       </x:c>
       <x:c r="H5" s="14" t="str">
-        <x:v>Əl ilə təsdiq tələb olunur</x:v>
+        <x:v>Dil 40 + ədəbiyyat 20×2; müəllim təsdiqlənərsə birlikdə ədədi orta hesablanmalıdır</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -698,7 +709,7 @@
         <x:v>nesimi-teacher-nergiz-quliyeva-agaqulu-qizi</x:v>
       </x:c>
       <x:c r="H7" s="14" t="str">
-        <x:v>Əl ilə təsdiq tələb olunur</x:v>
+        <x:v>Dil 40 + ədəbiyyat 20×2; müəllim təsdiqlənərsə birlikdə ədədi orta hesablanmalıdır</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -776,7 +787,7 @@
         <x:v>nesimi-teacher-ayten-qasimova-qasim-qizi</x:v>
       </x:c>
       <x:c r="H10" s="14" t="str">
-        <x:v>Əl ilə təsdiq tələb olunur</x:v>
+        <x:v>Dil 40 + ədəbiyyat 20×2; müəllim təsdiqlənərsə birlikdə ədədi orta hesablanmalıdır</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -897,7 +908,7 @@
         <x:v>8.75</x:v>
       </x:c>
       <x:c r="E15" s="15" t="n">
-        <x:v>6.5625</x:v>
+        <x:v>13.125</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
         <x:v>Nərgiz Quliyeva</x:v>
@@ -906,7 +917,7 @@
         <x:v>nesimi-teacher-nergiz-quliyeva-agaqulu-qizi</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str">
-        <x:v>Əl ilə təsdiq tələb olunur</x:v>
+        <x:v>Dil 40 + ədəbiyyat 20×2; müəllim təsdiqlənərsə birlikdə ədədi orta hesablanmalıdır</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1131,7 +1142,7 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="E24" s="15" t="n">
-        <x:v>1.875</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
         <x:v>Aytən Qasımova</x:v>
@@ -1140,7 +1151,7 @@
         <x:v>nesimi-teacher-ayten-qasimova-qasim-qizi</x:v>
       </x:c>
       <x:c r="H24" s="14" t="str">
-        <x:v>Əl ilə təsdiq tələb olunur</x:v>
+        <x:v>Dil 40 + ədəbiyyat 20×2; müəllim təsdiqlənərsə birlikdə ədədi orta hesablanmalıdır</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1157,7 +1168,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="E25" s="15" t="n">
-        <x:v>0.375</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
         <x:v>Səma Avilova</x:v>
@@ -1166,13 +1177,13 @@
         <x:v>nesimi-teacher-sema-avilova-fazil-qizi</x:v>
       </x:c>
       <x:c r="H25" s="14" t="str">
-        <x:v>Əl ilə təsdiq tələb olunur</x:v>
+        <x:v>Dil 40 + ədəbiyyat 20×2; müəllim təsdiqlənərsə birlikdə ədədi orta hesablanmalıdır</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb76f199828f44d75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f4d8b42913d4d4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1298,7 +1309,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1305b5b55484282"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d5274d68f014b10"/>
   </x:tableParts>
 </x:worksheet>
 </file>